--- a/astro-site/public/dl/plan-negocio-sushi-bar/checklist-apertura-sushi-bar.xlsx
+++ b/astro-site/public/dl/plan-negocio-sushi-bar/checklist-apertura-sushi-bar.xlsx
@@ -2538,7 +2538,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Con la calculadora del pescado, el arroz y el escandallo del pack: el coste de cada pieza y el margen en sala, para llevar y en plataforma. En plataforma el margen del combinado cae casi a la mitad</t>
+          <t>Con la calculadora del pescado, el arroz y el escandallo del pack: el coste de cada pieza y el margen en sala, para llevar y en plataforma. En plataforma el margen del combinado cae más de un cuarto</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-negocio-sushi-bar/checklist-apertura-sushi-bar.xlsx
+++ b/astro-site/public/dl/plan-negocio-sushi-bar/checklist-apertura-sushi-bar.xlsx
@@ -2077,7 +2077,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Si no eres tú el itamae (el jefe de barra que compra, limpia y corta el pescado), es la contratación difícil: las ofertas de sushiman van de 12.000 a 22.000 € brutos al año y las de un omakase pasan de 2.500 € al mes. Que los dos opinen sobre la barra y el frío antes de cerrar la obra: una baja del único que corta cierra la barra</t>
+          <t>Si no eres tú el itamae (el jefe de barra que compra, limpia y corta el pescado), es la contratación difícil: las ofertas de sushiman van de 12.000 a 22.000 € brutos al año y las de un omakase parten de 2.500 € al mes. Que los dos opinen sobre la barra y el frío antes de cerrar la obra: una baja del único que corta cierra la barra</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-negocio-sushi-bar/checklist-apertura-sushi-bar.xlsx
+++ b/astro-site/public/dl/plan-negocio-sushi-bar/checklist-apertura-sushi-bar.xlsx
@@ -1804,7 +1804,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Mide y anota el pH de cada tanda en la hoja 03 del Kit de Tareas Sushi Bar: su APPCC fija como límite crítico un pH de 4,6 o menos (criterio del Codex, no cifra legal); apunta a 4,2-4,3 para tener margen. Calibra el pH-metro con sus soluciones antes de empezar</t>
+          <t>Mide y anota el pH de cada tanda en la plantilla 02 del Kit de Tareas Sushi Bar: su APPCC fija como límite crítico un pH de 4,6 o menos (criterio del Codex, no cifra legal); apunta a 4,2-4,3 para tener margen. Calibra el pH-metro con sus soluciones antes de empezar</t>
         </is>
       </c>
     </row>
